--- a/04_Figures/F4/c_data/F4_supplementary.xlsx
+++ b/04_Figures/F4/c_data/F4_supplementary.xlsx
@@ -6850,7 +6850,7 @@
     <t xml:space="preserve">date_generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-27</t>
+    <t xml:space="preserve">2026-02-28</t>
   </si>
 </sst>
 </file>

--- a/04_Figures/F4/c_data/F4_supplementary.xlsx
+++ b/04_Figures/F4/c_data/F4_supplementary.xlsx
@@ -71881,7 +71881,7 @@
         <v>2279</v>
       </c>
       <c r="C4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
@@ -71892,7 +71892,7 @@
         <v>2280</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -71977,10 +71977,10 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>2279</v>
+        <v>2284</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -71988,10 +71988,10 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -71999,10 +71999,10 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>2285</v>
+        <v>2279</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
@@ -72010,9 +72010,20 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
         <v>2278</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C17" t="n">
         <v>9</v>
       </c>
     </row>
